--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="196">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,7 +304,7 @@
     <t>fr-lm-dicom-medication-administration.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
 </t>
   </si>
   <si>
@@ -317,6 +317,10 @@
     <t>fr-lm-dicom-medication-administration.header.author[x].authorOrganisation</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
     <t>L'auteur est une organisation</t>
   </si>
   <si>
@@ -326,7 +330,7 @@
     <t>fr-lm-dicom-medication-administration.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
 </t>
   </si>
   <si>
@@ -336,36 +340,59 @@
     <t>fr-lm-entry.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t>fr-lm-dicom-medication-administration.header.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-dicom-medication-administration.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.performer</t>
-  </si>
-  <si>
-    <t>fr-lm-dicom-medication-administration.header.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-dicom-medication-administration.header.participant[x]</t>
   </si>
   <si>
     <t>Participant</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.participant</t>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-dicom-medication-administration.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-dicom-medication-administration.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-dicom-medication-administration.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
   </si>
   <si>
     <t>fr-lm-dicom-medication-administration.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -388,11 +415,26 @@
     <t>fr-lm-entry.header.date</t>
   </si>
   <si>
-    <t>fr-lm-dicom-medication-administration.header.source</t>
+    <t>fr-lm-dicom-medication-administration.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-dicom-medication-administration.header.source</t>
   </si>
   <si>
     <t>Source</t>
@@ -410,16 +452,6 @@
   </si>
   <si>
     <t>fr-lm-entry.header.langue</t>
-  </si>
-  <si>
-    <t>fr-lm-dicom-medication-administration.statut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Statut de l'entrée</t>
   </si>
   <si>
     <t>fr-lm-dicom-medication-administration.voieAdministration</t>
@@ -892,7 +924,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ29"/>
+  <dimension ref="A1:AJ32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="71.734375" customWidth="true" bestFit="true"/>
@@ -905,7 +937,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -920,7 +952,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="68.90234375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -1670,13 +1702,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1727,7 +1759,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1744,10 +1776,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1770,13 +1802,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1827,7 +1859,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1844,10 +1876,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1870,13 +1902,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1927,7 +1959,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1944,10 +1976,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1970,7 +2002,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>111</v>
@@ -2070,13 +2102,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2127,7 +2159,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2144,10 +2176,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2158,7 +2190,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2170,13 +2202,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2227,13 +2259,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2244,10 +2276,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2258,7 +2290,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2270,13 +2302,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2327,13 +2359,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2344,10 +2376,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2358,7 +2390,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2370,13 +2402,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2427,13 +2459,13 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>73</v>
@@ -2444,10 +2476,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2455,7 +2487,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2470,13 +2502,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2527,10 +2559,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2544,10 +2576,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2555,7 +2587,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -2570,7 +2602,7 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>132</v>
@@ -2609,7 +2641,7 @@
         <v>133</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2627,10 +2659,10 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2644,10 +2676,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2670,13 +2702,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2727,7 +2759,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2744,10 +2776,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2770,13 +2802,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2827,7 +2859,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2844,10 +2876,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2855,7 +2887,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>79</v>
@@ -2870,13 +2902,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2906,7 +2938,7 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>73</v>
@@ -2927,10 +2959,10 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>79</v>
@@ -2944,10 +2976,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2955,7 +2987,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -2970,13 +3002,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3027,10 +3059,10 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -3044,10 +3076,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3070,13 +3102,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3106,7 +3138,7 @@
         <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>73</v>
@@ -3127,7 +3159,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3139,15 +3171,15 @@
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>147</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3155,7 +3187,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>79</v>
@@ -3170,13 +3202,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3227,10 +3259,10 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>79</v>
@@ -3251,14 +3283,14 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>73</v>
@@ -3270,17 +3302,15 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>73</v>
@@ -3317,39 +3347,39 @@
         <v>73</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>159</v>
+        <v>73</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>161</v>
+        <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>163</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3360,7 +3390,7 @@
         <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>73</v>
@@ -3369,23 +3399,19 @@
         <v>73</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>73</v>
       </c>
@@ -3412,7 +3438,7 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>73</v>
@@ -3433,27 +3459,27 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3473,23 +3499,19 @@
         <v>73</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>73</v>
       </c>
@@ -3537,7 +3559,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3549,26 +3571,26 @@
         <v>73</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>147</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>73</v>
@@ -3580,15 +3602,17 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>73</v>
@@ -3616,7 +3640,7 @@
         <v>73</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>180</v>
+        <v>73</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>73</v>
@@ -3625,39 +3649,39 @@
         <v>73</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>73</v>
+        <v>172</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>73</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3668,7 +3692,7 @@
         <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>73</v>
@@ -3677,19 +3701,23 @@
         <v>73</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>73</v>
       </c>
@@ -3737,19 +3765,19 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>73</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29">
@@ -3777,19 +3805,23 @@
         <v>73</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>184</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>73</v>
       </c>
@@ -3837,7 +3869,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3849,6 +3881,306 @@
         <v>73</v>
       </c>
       <c r="AJ29" t="s" s="2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
